--- a/Documents/Product Catalog/Full Product Catalog/home funiture.xlsx
+++ b/Documents/Product Catalog/Full Product Catalog/home funiture.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Talukder Furniture\Documents\Product Catalog\Full Product Catalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\By Raj\Talukder Furniture\Documents\Product Catalog\Full Product Catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B11771-461E-48FE-A98F-AF36F7BCE0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CB71B6-189B-472C-84DB-5D2A312A62F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4339" uniqueCount="1480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4339" uniqueCount="1473">
   <si>
     <t>Talukder Furniture Ltd.</t>
   </si>
@@ -7039,12 +7039,6 @@
     <t>সূর্যমুখী বেড সাইড টেবিল</t>
   </si>
   <si>
-    <t>ডাবল বেড</t>
-  </si>
-  <si>
-    <t>বেড সাইড টেবিল</t>
-  </si>
-  <si>
     <t>মিতালী ডাবল বেড</t>
   </si>
   <si>
@@ -7069,9 +7063,6 @@
     <t>মুক্তালী বেড সাইড টেবিল</t>
   </si>
   <si>
-    <t>বেড</t>
-  </si>
-  <si>
     <t>চারুলতা ড্রেসিং টেবিল</t>
   </si>
   <si>
@@ -7093,9 +7084,6 @@
     <t>শুভ্রা ড্রেসিং টেবিল</t>
   </si>
   <si>
-    <t>ড্রেসিং টেবিল</t>
-  </si>
-  <si>
     <t>রূপান্তর ড্রেসিং টেবিল</t>
   </si>
   <si>
@@ -7156,9 +7144,6 @@
     <t>মুক্তালী ২-ডোর কাপবোর্ড</t>
   </si>
   <si>
-    <t>২-ডোর কাপবোর্ড</t>
-  </si>
-  <si>
     <t>বনলতা ২-ডোর কাপবোর্ড</t>
   </si>
   <si>
@@ -7183,54 +7168,12 @@
     <t>রেখাচিত্র ২-ডোর কাপবোর্ড</t>
   </si>
   <si>
-    <t>৩-ডোর কাপবোর্ড</t>
-  </si>
-  <si>
-    <t>শুভ্রা ওয়ারড্রোব</t>
-  </si>
-  <si>
-    <t>বিপরীত ওয়ারড্রোব</t>
-  </si>
-  <si>
-    <t>কদম্বরী ওয়ারড্রোব</t>
-  </si>
-  <si>
-    <t>দিগন্ত ওয়ারড্রোব</t>
-  </si>
-  <si>
-    <t>রেখাচিত্র ওয়ারড্রোব</t>
-  </si>
-  <si>
-    <t>চেস্ট অফ ড্রয়ার</t>
-  </si>
-  <si>
-    <t>ওয়ারড্রোব</t>
-  </si>
-  <si>
     <t>রূপান্তর ওয়ারড্রোব</t>
   </si>
   <si>
     <t>মুক্তালী চেস্ট অফ ড্রয়ার</t>
   </si>
   <si>
-    <t>বনলতা ওয়ারড্রোব</t>
-  </si>
-  <si>
-    <t>চারুলতা ওয়ারড্রোব</t>
-  </si>
-  <si>
-    <t>অম্বরী ওয়ারড্রোব</t>
-  </si>
-  <si>
-    <t>শিল্পিক ওয়ারড্রোব</t>
-  </si>
-  <si>
-    <t>পদ্ম ওয়ারড্রোব</t>
-  </si>
-  <si>
-    <t>অরণ্য ওয়ারড্রোব</t>
-  </si>
-  <si>
     <t>পদ্ম আলনা</t>
   </si>
   <si>
@@ -7258,97 +7201,133 @@
     <t>অরণ্য Shoe Rack</t>
   </si>
   <si>
-    <t>পদ্ম Divan</t>
-  </si>
-  <si>
-    <t>শিল্পিক Divan</t>
-  </si>
-  <si>
-    <t>অরণ্য Divan</t>
-  </si>
-  <si>
-    <t>ফ্লোরাল Sofa</t>
-  </si>
-  <si>
     <t>পদ্ম Oven Shelf</t>
   </si>
   <si>
-    <t>পদ্ম Dining Talbe</t>
-  </si>
-  <si>
-    <t>পদ্ম Dining Chair</t>
-  </si>
-  <si>
-    <t>শিল্পিক Dining Talbe</t>
-  </si>
-  <si>
-    <t>শিল্পিক Dining Chair</t>
-  </si>
-  <si>
-    <t>রেখাচিত্র Dining Table</t>
-  </si>
-  <si>
-    <t>কদম্বরী Dining Table</t>
-  </si>
-  <si>
-    <t>কদম্বরী Dining Chair</t>
-  </si>
-  <si>
-    <t>রেখাচিত্র Dining Chair</t>
-  </si>
-  <si>
     <t>পদ্ম Showcase</t>
   </si>
   <si>
     <t>শিল্পিক Showcase</t>
   </si>
   <si>
-    <t>শুভ্রা Dinner Wagon</t>
-  </si>
-  <si>
-    <t>বনলতা TV Cabinet</t>
-  </si>
-  <si>
-    <t>শুভ্রা TV Cabinet</t>
-  </si>
-  <si>
-    <t>কদম্বরী TV Cabinet</t>
-  </si>
-  <si>
-    <t>বিপরীত TV Cabinet</t>
-  </si>
-  <si>
-    <t>শুভ্রা Shoe Rack</t>
-  </si>
-  <si>
-    <t>বনলতা Shoe Rack</t>
-  </si>
-  <si>
-    <t>বনলতা Reading Table</t>
-  </si>
-  <si>
-    <t>শুভ্রা Reading Table</t>
-  </si>
-  <si>
-    <t>বনলতা বেড</t>
-  </si>
-  <si>
-    <t>বনলতা 2-Door Steel Almirah</t>
-  </si>
-  <si>
-    <t>শুভ্রা 2-Door Steel Almirah</t>
-  </si>
-  <si>
-    <t>বিপরীত 2-Door Steel Almirah</t>
-  </si>
-  <si>
-    <t>কদম্বরী 2-Door Steel Almirah</t>
-  </si>
-  <si>
-    <t>দিগন্ত 2-Door Steel Almirah</t>
-  </si>
-  <si>
-    <t>রেখাচিত্র 2-Door Steel Almirah</t>
+    <t>ফ্লোরাল ডাবল বেড</t>
+  </si>
+  <si>
+    <t>ফ্লোরাল বেড সাইড টেবিল</t>
+  </si>
+  <si>
+    <t>রৌজা ডাবল বেড</t>
+  </si>
+  <si>
+    <t>রৌজা বেড সাইড টেবিল</t>
+  </si>
+  <si>
+    <t>কসমস ডাবল বেড</t>
+  </si>
+  <si>
+    <t>কসমস বেড সাইড টেবিল</t>
+  </si>
+  <si>
+    <t>স্বর্ণালী বেড</t>
+  </si>
+  <si>
+    <t>স্বর্ণালী বেড সাইড টেবিল</t>
+  </si>
+  <si>
+    <t>স্বর্ণালী ড্রেসিং টেবিল</t>
+  </si>
+  <si>
+    <t>অবয়ব ড্রেসিং টেবিল</t>
+  </si>
+  <si>
+    <t>সূর্যমুখী ড্রেসিং টেবিল</t>
+  </si>
+  <si>
+    <t>কসমস ড্রেসিং টেবিল</t>
+  </si>
+  <si>
+    <t>স্বর্ণালী ২-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>অবয়ব ২-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>অবয়ব ৩-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>সূর্যমুখী ২-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>সূর্যমুখী ৩-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>কসমস ২-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>কসমস ৩-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>স্বর্ণালী ওয়ারড্রোব</t>
+  </si>
+  <si>
+    <t>সানরে বেড</t>
+  </si>
+  <si>
+    <t>প্রিন্সেস বেড</t>
+  </si>
+  <si>
+    <t>হ্যালো কিটি বেড</t>
+  </si>
+  <si>
+    <t>স্কাইবো বেড</t>
+  </si>
+  <si>
+    <t>পোকো বেড</t>
+  </si>
+  <si>
+    <t>মোয়ানা মোয়ানা বেড</t>
+  </si>
+  <si>
+    <t>Divan</t>
+  </si>
+  <si>
+    <t>Dining Talbe</t>
+  </si>
+  <si>
+    <t>Dinner Wagon</t>
+  </si>
+  <si>
+    <t>অবয়ব ডাবল বেড</t>
+  </si>
+  <si>
+    <t>অবয়ব বেড সাইড টেবিল</t>
+  </si>
+  <si>
+    <t>Bed</t>
+  </si>
+  <si>
+    <t>Bed Side Table</t>
+  </si>
+  <si>
+    <t>Dressing Table</t>
+  </si>
+  <si>
+    <t>2-Door Cupboard</t>
+  </si>
+  <si>
+    <t>3-Door Cupboard</t>
+  </si>
+  <si>
+    <t>Wardrobe</t>
+  </si>
+  <si>
+    <t>Chest of Drawer</t>
+  </si>
+  <si>
+    <t>অবয়ব চেস্ট অফ ড্রয়ার</t>
+  </si>
+  <si>
+    <t>অবয়ব 2-Door Steel Almirah</t>
   </si>
 </sst>
 </file>
@@ -29102,7 +29081,7 @@
         <v>127</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1374</v>
+        <v>1433</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="13" t="s">
@@ -29179,7 +29158,7 @@
         <v>132</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1375</v>
+        <v>1434</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="13" t="s">
@@ -29256,7 +29235,7 @@
         <v>136</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1376</v>
+        <v>1435</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="13" t="s">
@@ -29333,7 +29312,7 @@
         <v>139</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1377</v>
+        <v>1436</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="13" t="s">
@@ -29410,7 +29389,7 @@
         <v>142</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1376</v>
+        <v>1437</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="13" t="s">
@@ -29487,7 +29466,7 @@
         <v>145</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1377</v>
+        <v>1438</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="13" t="s">
@@ -29564,7 +29543,7 @@
         <v>148</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="13" t="s">
@@ -29641,7 +29620,7 @@
         <v>151</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="13" t="s">
@@ -29718,7 +29697,7 @@
         <v>154</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1376</v>
+        <v>1462</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="13" t="s">
@@ -29795,7 +29774,7 @@
         <v>160</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1377</v>
+        <v>1463</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="13" t="s">
@@ -29872,7 +29851,7 @@
         <v>164</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="11" t="s">
@@ -29949,7 +29928,7 @@
         <v>164</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="11" t="s">
@@ -30026,7 +30005,7 @@
         <v>164</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="D47" s="26"/>
       <c r="E47" s="11" t="s">
@@ -30103,7 +30082,7 @@
         <v>176</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="11" t="s">
@@ -30180,7 +30159,7 @@
         <v>176</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="11" t="s">
@@ -30257,7 +30236,7 @@
         <v>176</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="11" t="s">
@@ -30334,7 +30313,7 @@
         <v>186</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="11" t="s">
@@ -30411,7 +30390,7 @@
         <v>190</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="11" t="s">
@@ -30488,7 +30467,7 @@
         <v>190</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="11" t="s">
@@ -30565,7 +30544,7 @@
         <v>190</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="11" t="s">
@@ -30642,7 +30621,7 @@
         <v>200</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="11" t="s">
@@ -30719,7 +30698,7 @@
         <v>200</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="11" t="s">
@@ -30796,7 +30775,7 @@
         <v>200</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D57" s="12"/>
       <c r="E57" s="11" t="s">
@@ -30873,7 +30852,7 @@
         <v>210</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D58" s="12"/>
       <c r="E58" s="11" t="s">
@@ -30950,7 +30929,7 @@
         <v>210</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D59" s="12"/>
       <c r="E59" s="11" t="s">
@@ -31027,7 +31006,7 @@
         <v>210</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D60" s="12"/>
       <c r="E60" s="11" t="s">
@@ -31104,7 +31083,7 @@
         <v>217</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="D61" s="12"/>
       <c r="E61" s="11" t="s">
@@ -31181,7 +31160,7 @@
         <v>220</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1386</v>
+        <v>1439</v>
       </c>
       <c r="D62" s="12"/>
       <c r="E62" s="11" t="s">
@@ -31258,7 +31237,7 @@
         <v>220</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1386</v>
+        <v>1439</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="11" t="s">
@@ -31307,7 +31286,7 @@
         <v>220</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1386</v>
+        <v>1439</v>
       </c>
       <c r="D64" s="12"/>
       <c r="E64" s="11" t="s">
@@ -31356,7 +31335,7 @@
         <v>227</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1377</v>
+        <v>1440</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="11" t="s">
@@ -31405,7 +31384,7 @@
         <v>230</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="11" t="s">
@@ -31454,7 +31433,7 @@
         <v>230</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D67" s="12"/>
       <c r="E67" s="11" t="s">
@@ -31503,7 +31482,7 @@
         <v>230</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D68" s="12"/>
       <c r="E68" s="11" t="s">
@@ -31552,7 +31531,7 @@
         <v>240</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1377</v>
+        <v>1465</v>
       </c>
       <c r="D69" s="12"/>
       <c r="E69" s="11" t="s">
@@ -31601,7 +31580,7 @@
         <v>244</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="11" t="s">
@@ -31650,7 +31629,7 @@
         <v>244</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D71" s="12"/>
       <c r="E71" s="11" t="s">
@@ -31699,7 +31678,7 @@
         <v>244</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D72" s="12"/>
       <c r="E72" s="11" t="s">
@@ -31748,7 +31727,7 @@
         <v>254</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>1377</v>
+        <v>1465</v>
       </c>
       <c r="D73" s="12"/>
       <c r="E73" s="11" t="s">
@@ -31797,7 +31776,7 @@
         <v>258</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D74" s="12"/>
       <c r="E74" s="11" t="s">
@@ -31846,7 +31825,7 @@
         <v>258</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D75" s="12"/>
       <c r="E75" s="11" t="s">
@@ -31895,7 +31874,7 @@
         <v>258</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D76" s="12"/>
       <c r="E76" s="11" t="s">
@@ -31944,7 +31923,7 @@
         <v>268</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>1377</v>
+        <v>1465</v>
       </c>
       <c r="D77" s="12"/>
       <c r="E77" s="11" t="s">
@@ -31993,7 +31972,7 @@
         <v>272</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D78" s="12"/>
       <c r="E78" s="11" t="s">
@@ -32042,7 +32021,7 @@
         <v>272</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D79" s="12"/>
       <c r="E79" s="11" t="s">
@@ -32091,7 +32070,7 @@
         <v>272</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D80" s="12"/>
       <c r="E80" s="11" t="s">
@@ -32140,7 +32119,7 @@
         <v>284</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>1377</v>
+        <v>1465</v>
       </c>
       <c r="D81" s="12"/>
       <c r="E81" s="11" t="s">
@@ -32189,7 +32168,7 @@
         <v>288</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D82" s="12"/>
       <c r="E82" s="11" t="s">
@@ -32238,7 +32217,7 @@
         <v>288</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D83" s="12"/>
       <c r="E83" s="11" t="s">
@@ -32287,7 +32266,7 @@
         <v>288</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D84" s="12"/>
       <c r="E84" s="11" t="s">
@@ -32336,7 +32315,7 @@
         <v>298</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>1377</v>
+        <v>1465</v>
       </c>
       <c r="D85" s="12"/>
       <c r="E85" s="11" t="s">
@@ -32385,7 +32364,7 @@
         <v>302</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D86" s="12"/>
       <c r="E86" s="11" t="s">
@@ -32434,7 +32413,7 @@
         <v>302</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D87" s="12"/>
       <c r="E87" s="11" t="s">
@@ -32483,7 +32462,7 @@
         <v>302</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D88" s="12"/>
       <c r="E88" s="11" t="s">
@@ -32532,7 +32511,7 @@
         <v>312</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>1377</v>
+        <v>1465</v>
       </c>
       <c r="D89" s="12"/>
       <c r="E89" s="11" t="s">
@@ -32581,7 +32560,7 @@
         <v>316</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D90" s="12"/>
       <c r="E90" s="11" t="s">
@@ -32630,7 +32609,7 @@
         <v>316</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D91" s="12"/>
       <c r="E91" s="11" t="s">
@@ -32679,7 +32658,7 @@
         <v>316</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D92" s="12"/>
       <c r="E92" s="11" t="s">
@@ -32728,7 +32707,7 @@
         <v>323</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>1377</v>
+        <v>1465</v>
       </c>
       <c r="D93" s="12"/>
       <c r="E93" s="11" t="s">
@@ -32777,7 +32756,7 @@
         <v>326</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D94" s="12"/>
       <c r="E94" s="11" t="s">
@@ -32826,7 +32805,7 @@
         <v>326</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D95" s="12"/>
       <c r="E95" s="11" t="s">
@@ -32875,7 +32854,7 @@
         <v>326</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="11" t="s">
@@ -32924,7 +32903,7 @@
         <v>337</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>1377</v>
+        <v>1465</v>
       </c>
       <c r="D97" s="12"/>
       <c r="E97" s="11" t="s">
@@ -32973,7 +32952,7 @@
         <v>340</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="D98" s="12"/>
       <c r="E98" s="13" t="s">
@@ -33022,7 +33001,7 @@
         <v>344</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="D99" s="12"/>
       <c r="E99" s="13" t="s">
@@ -33071,7 +33050,7 @@
         <v>347</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="D100" s="12"/>
       <c r="E100" s="13" t="s">
@@ -33120,7 +33099,7 @@
         <v>350</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="13" t="s">
@@ -33169,7 +33148,7 @@
         <v>353</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="D102" s="12"/>
       <c r="E102" s="13" t="s">
@@ -33218,7 +33197,7 @@
         <v>356</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="D103" s="12"/>
       <c r="E103" s="13" t="s">
@@ -33267,7 +33246,7 @@
         <v>360</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="D104" s="12"/>
       <c r="E104" s="13" t="s">
@@ -33316,7 +33295,7 @@
         <v>364</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="D105" s="12"/>
       <c r="E105" s="11" t="s">
@@ -33365,7 +33344,7 @@
         <v>368</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="D106" s="12"/>
       <c r="E106" s="11" t="s">
@@ -33414,7 +33393,7 @@
         <v>372</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="D107" s="12"/>
       <c r="E107" s="11" t="s">
@@ -33463,7 +33442,7 @@
         <v>376</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="D108" s="12"/>
       <c r="E108" s="11" t="s">
@@ -33512,7 +33491,7 @@
         <v>379</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>1394</v>
+        <v>1441</v>
       </c>
       <c r="D109" s="12"/>
       <c r="E109" s="11" t="s">
@@ -33561,7 +33540,7 @@
         <v>382</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="D110" s="12"/>
       <c r="E110" s="11" t="s">
@@ -33610,7 +33589,7 @@
         <v>386</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="D111" s="12"/>
       <c r="E111" s="11" t="s">
@@ -33659,7 +33638,7 @@
         <v>390</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="D112" s="12"/>
       <c r="E112" s="11" t="s">
@@ -33708,7 +33687,7 @@
         <v>394</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="D113" s="12"/>
       <c r="E113" s="11" t="s">
@@ -33757,7 +33736,7 @@
         <v>397</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="D114" s="12"/>
       <c r="E114" s="11" t="s">
@@ -33806,7 +33785,7 @@
         <v>401</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="D115" s="12"/>
       <c r="E115" s="11" t="s">
@@ -33855,7 +33834,7 @@
         <v>404</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="D116" s="12"/>
       <c r="E116" s="13" t="s">
@@ -33904,7 +33883,7 @@
         <v>360</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="D117" s="12"/>
       <c r="E117" s="13" t="s">
@@ -33953,7 +33932,7 @@
         <v>411</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="D118" s="12"/>
       <c r="E118" s="13" t="s">
@@ -34002,7 +33981,7 @@
         <v>416</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="D119" s="12"/>
       <c r="E119" s="13" t="s">
@@ -34051,7 +34030,7 @@
         <v>420</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="D120" s="12"/>
       <c r="E120" s="13" t="s">
@@ -34100,7 +34079,7 @@
         <v>423</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="D121" s="12"/>
       <c r="E121" s="13" t="s">
@@ -34149,7 +34128,7 @@
         <v>427</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="D122" s="12"/>
       <c r="E122" s="13" t="s">
@@ -34198,7 +34177,7 @@
         <v>431</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>1394</v>
+        <v>1442</v>
       </c>
       <c r="D123" s="12"/>
       <c r="E123" s="13" t="s">
@@ -34247,7 +34226,7 @@
         <v>434</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>1394</v>
+        <v>1443</v>
       </c>
       <c r="D124" s="12"/>
       <c r="E124" s="13" t="s">
@@ -34296,7 +34275,7 @@
         <v>437</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>1394</v>
+        <v>1444</v>
       </c>
       <c r="D125" s="12"/>
       <c r="E125" s="13" t="s">
@@ -34345,7 +34324,7 @@
         <v>441</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="D126" s="12"/>
       <c r="E126" s="13" t="s">
@@ -34394,7 +34373,7 @@
         <v>445</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="D127" s="12"/>
       <c r="E127" s="13" t="s">
@@ -34443,7 +34422,7 @@
         <v>449</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="D128" s="12"/>
       <c r="E128" s="13" t="s">
@@ -34492,7 +34471,7 @@
         <v>453</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="D129" s="12"/>
       <c r="E129" s="13" t="s">
@@ -34541,7 +34520,7 @@
         <v>453</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="D130" s="12"/>
       <c r="E130" s="13" t="s">
@@ -34590,7 +34569,7 @@
         <v>453</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="D131" s="12"/>
       <c r="E131" s="13" t="s">
@@ -34639,7 +34618,7 @@
         <v>463</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="D132" s="12"/>
       <c r="E132" s="13" t="s">
@@ -34688,7 +34667,7 @@
         <v>463</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="D133" s="12"/>
       <c r="E133" s="13" t="s">
@@ -34737,7 +34716,7 @@
         <v>469</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="D134" s="12"/>
       <c r="E134" s="13" t="s">
@@ -34786,7 +34765,7 @@
         <v>469</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="D135" s="12"/>
       <c r="E135" s="13" t="s">
@@ -34835,7 +34814,7 @@
         <v>474</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="D136" s="12"/>
       <c r="E136" s="13" t="s">
@@ -34884,7 +34863,7 @@
         <v>474</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="D137" s="12"/>
       <c r="E137" s="13" t="s">
@@ -34933,7 +34912,7 @@
         <v>474</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="D138" s="12"/>
       <c r="E138" s="13" t="s">
@@ -34982,7 +34961,7 @@
         <v>445</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="D139" s="12"/>
       <c r="E139" s="13" t="s">
@@ -35031,7 +35010,7 @@
         <v>445</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="D140" s="12"/>
       <c r="E140" s="13" t="s">
@@ -35080,7 +35059,7 @@
         <v>445</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="D141" s="12"/>
       <c r="E141" s="13" t="s">
@@ -35129,7 +35108,7 @@
         <v>487</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="D142" s="12"/>
       <c r="E142" s="11" t="s">
@@ -35178,7 +35157,7 @@
         <v>491</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="D143" s="12"/>
       <c r="E143" s="11" t="s">
@@ -35227,7 +35206,7 @@
         <v>494</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>1415</v>
+        <v>1445</v>
       </c>
       <c r="D144" s="12"/>
       <c r="E144" s="11" t="s">
@@ -35276,7 +35255,7 @@
         <v>498</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>1415</v>
+        <v>1467</v>
       </c>
       <c r="D145" s="12"/>
       <c r="E145" s="11" t="s">
@@ -35325,7 +35304,7 @@
         <v>502</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>1415</v>
+        <v>1467</v>
       </c>
       <c r="D146" s="12"/>
       <c r="E146" s="11" t="s">
@@ -35374,7 +35353,7 @@
         <v>506</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>1415</v>
+        <v>1467</v>
       </c>
       <c r="D147" s="12"/>
       <c r="E147" s="11" t="s">
@@ -35423,7 +35402,7 @@
         <v>510</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>1415</v>
+        <v>1467</v>
       </c>
       <c r="D148" s="12"/>
       <c r="E148" s="11" t="s">
@@ -35472,7 +35451,7 @@
         <v>513</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>1415</v>
+        <v>1467</v>
       </c>
       <c r="D149" s="12"/>
       <c r="E149" s="11" t="s">
@@ -35668,7 +35647,7 @@
         <v>528</v>
       </c>
       <c r="C153" s="32" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="D153" s="33"/>
       <c r="E153" s="34" t="s">
@@ -35718,7 +35697,7 @@
         <v>528</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="D154" s="12"/>
       <c r="E154" s="13" t="s">
@@ -35767,7 +35746,7 @@
         <v>534</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="D155" s="12"/>
       <c r="E155" s="13" t="s">
@@ -35816,7 +35795,7 @@
         <v>538</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="D156" s="12"/>
       <c r="E156" s="13" t="s">
@@ -35865,7 +35844,7 @@
         <v>543</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="D157" s="12"/>
       <c r="E157" s="13" t="s">
@@ -35914,7 +35893,7 @@
         <v>543</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="D158" s="12"/>
       <c r="E158" s="13" t="s">
@@ -35963,7 +35942,7 @@
         <v>548</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="D159" s="12"/>
       <c r="E159" s="13" t="s">
@@ -36012,7 +35991,7 @@
         <v>548</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="D160" s="12"/>
       <c r="E160" s="13" t="s">
@@ -36061,7 +36040,7 @@
         <v>556</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="D161" s="12"/>
       <c r="E161" s="13" t="s">
@@ -36110,7 +36089,7 @@
         <v>559</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>1424</v>
+        <v>1468</v>
       </c>
       <c r="D162" s="12"/>
       <c r="E162" s="13" t="s">
@@ -36159,7 +36138,7 @@
         <v>563</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>1415</v>
+        <v>1467</v>
       </c>
       <c r="D163" s="12"/>
       <c r="E163" s="13" t="s">
@@ -36208,7 +36187,7 @@
         <v>563</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>1424</v>
+        <v>1468</v>
       </c>
       <c r="D164" s="12"/>
       <c r="E164" s="13" t="s">
@@ -36257,7 +36236,7 @@
         <v>569</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>1415</v>
+        <v>1467</v>
       </c>
       <c r="D165" s="12"/>
       <c r="E165" s="13" t="s">
@@ -36306,7 +36285,7 @@
         <v>569</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>1424</v>
+        <v>1468</v>
       </c>
       <c r="D166" s="12"/>
       <c r="E166" s="13" t="s">
@@ -36355,7 +36334,7 @@
         <v>569</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>1424</v>
+        <v>1468</v>
       </c>
       <c r="D167" s="12"/>
       <c r="E167" s="13" t="s">
@@ -36404,7 +36383,7 @@
         <v>576</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>1415</v>
+        <v>1446</v>
       </c>
       <c r="D168" s="12"/>
       <c r="E168" s="13" t="s">
@@ -36453,7 +36432,7 @@
         <v>576</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>1424</v>
+        <v>1447</v>
       </c>
       <c r="D169" s="12"/>
       <c r="E169" s="13" t="s">
@@ -36502,7 +36481,7 @@
         <v>576</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>1424</v>
+        <v>1447</v>
       </c>
       <c r="D170" s="12"/>
       <c r="E170" s="13" t="s">
@@ -36551,7 +36530,7 @@
         <v>585</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>1415</v>
+        <v>1448</v>
       </c>
       <c r="D171" s="12"/>
       <c r="E171" s="13" t="s">
@@ -36600,7 +36579,7 @@
         <v>585</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>1424</v>
+        <v>1449</v>
       </c>
       <c r="D172" s="12"/>
       <c r="E172" s="13" t="s">
@@ -36649,7 +36628,7 @@
         <v>585</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>1424</v>
+        <v>1449</v>
       </c>
       <c r="D173" s="12"/>
       <c r="E173" s="13" t="s">
@@ -36698,7 +36677,7 @@
         <v>592</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>1415</v>
+        <v>1450</v>
       </c>
       <c r="D174" s="12"/>
       <c r="E174" s="13" t="s">
@@ -36747,7 +36726,7 @@
         <v>592</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>1424</v>
+        <v>1451</v>
       </c>
       <c r="D175" s="12"/>
       <c r="E175" s="13" t="s">
@@ -36796,7 +36775,7 @@
         <v>592</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>1424</v>
+        <v>1451</v>
       </c>
       <c r="D176" s="12"/>
       <c r="E176" s="13" t="s">
@@ -36845,7 +36824,7 @@
         <v>599</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>1415</v>
+        <v>1467</v>
       </c>
       <c r="D177" s="12"/>
       <c r="E177" s="13" t="s">
@@ -36894,7 +36873,7 @@
         <v>604</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>1425</v>
+        <v>1469</v>
       </c>
       <c r="D178" s="12"/>
       <c r="E178" s="13" t="s">
@@ -36943,7 +36922,7 @@
         <v>608</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>1425</v>
+        <v>1469</v>
       </c>
       <c r="D179" s="12"/>
       <c r="E179" s="13" t="s">
@@ -36992,7 +36971,7 @@
         <v>612</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>1426</v>
+        <v>1469</v>
       </c>
       <c r="D180" s="12"/>
       <c r="E180" s="13" t="s">
@@ -37041,7 +37020,7 @@
         <v>616</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>1427</v>
+        <v>1469</v>
       </c>
       <c r="D181" s="12"/>
       <c r="E181" s="13" t="s">
@@ -37090,7 +37069,7 @@
         <v>620</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>1428</v>
+        <v>1469</v>
       </c>
       <c r="D182" s="12"/>
       <c r="E182" s="13" t="s">
@@ -37139,7 +37118,7 @@
         <v>625</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>1429</v>
+        <v>1469</v>
       </c>
       <c r="D183" s="12"/>
       <c r="E183" s="13" t="s">
@@ -37188,7 +37167,7 @@
         <v>629</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>1430</v>
+        <v>1470</v>
       </c>
       <c r="D184" s="12"/>
       <c r="E184" s="13" t="s">
@@ -37237,7 +37216,7 @@
         <v>632</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>1430</v>
+        <v>1470</v>
       </c>
       <c r="D185" s="12"/>
       <c r="E185" s="13" t="s">
@@ -37286,7 +37265,7 @@
         <v>636</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>1430</v>
+        <v>1470</v>
       </c>
       <c r="D186" s="12"/>
       <c r="E186" s="13" t="s">
@@ -37335,7 +37314,7 @@
         <v>639</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>1430</v>
+        <v>1470</v>
       </c>
       <c r="D187" s="12"/>
       <c r="E187" s="13" t="s">
@@ -37384,7 +37363,7 @@
         <v>642</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>1430</v>
+        <v>1471</v>
       </c>
       <c r="D188" s="12"/>
       <c r="E188" s="13" t="s">
@@ -37433,7 +37412,7 @@
         <v>646</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D189" s="12"/>
       <c r="E189" s="11" t="s">
@@ -37482,7 +37461,7 @@
         <v>632</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D190" s="12"/>
       <c r="E190" s="11" t="s">
@@ -37531,7 +37510,7 @@
         <v>636</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D191" s="12"/>
       <c r="E191" s="11" t="s">
@@ -37580,7 +37559,7 @@
         <v>639</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D192" s="12"/>
       <c r="E192" s="11" t="s">
@@ -37629,7 +37608,7 @@
         <v>655</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>1432</v>
+        <v>1419</v>
       </c>
       <c r="D193" s="12"/>
       <c r="E193" s="11" t="s">
@@ -37678,7 +37657,7 @@
         <v>659</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>1433</v>
+        <v>1420</v>
       </c>
       <c r="D194" s="12"/>
       <c r="E194" s="11" t="s">
@@ -37727,7 +37706,7 @@
         <v>662</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>1431</v>
+        <v>1452</v>
       </c>
       <c r="D195" s="12"/>
       <c r="E195" s="11" t="s">
@@ -37776,7 +37755,7 @@
         <v>666</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D196" s="12"/>
       <c r="E196" s="11" t="s">
@@ -37825,7 +37804,7 @@
         <v>669</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D197" s="12"/>
       <c r="E197" s="11" t="s">
@@ -37874,7 +37853,7 @@
         <v>673</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>1434</v>
+        <v>1469</v>
       </c>
       <c r="D198" s="12"/>
       <c r="E198" s="13" t="s">
@@ -37923,7 +37902,7 @@
         <v>677</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D199" s="12"/>
       <c r="E199" s="11" t="s">
@@ -37972,7 +37951,7 @@
         <v>681</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D200" s="12"/>
       <c r="E200" s="11" t="s">
@@ -38021,7 +38000,7 @@
         <v>685</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D201" s="12"/>
       <c r="E201" s="11" t="s">
@@ -38070,7 +38049,7 @@
         <v>689</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D202" s="12"/>
       <c r="E202" s="11" t="s">
@@ -38119,7 +38098,7 @@
         <v>692</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D203" s="12"/>
       <c r="E203" s="11" t="s">
@@ -38168,7 +38147,7 @@
         <v>696</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D204" s="12"/>
       <c r="E204" s="11" t="s">
@@ -38217,7 +38196,7 @@
         <v>700</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D205" s="12"/>
       <c r="E205" s="11" t="s">
@@ -38266,7 +38245,7 @@
         <v>704</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>1435</v>
+        <v>1469</v>
       </c>
       <c r="D206" s="12"/>
       <c r="E206" s="13" t="s">
@@ -38315,7 +38294,7 @@
         <v>708</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>1436</v>
+        <v>1469</v>
       </c>
       <c r="D207" s="12"/>
       <c r="E207" s="13" t="s">
@@ -38364,7 +38343,7 @@
         <v>711</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>1437</v>
+        <v>1469</v>
       </c>
       <c r="D208" s="12"/>
       <c r="E208" s="13" t="s">
@@ -38413,7 +38392,7 @@
         <v>714</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>1438</v>
+        <v>1469</v>
       </c>
       <c r="D209" s="12"/>
       <c r="E209" s="13" t="s">
@@ -38462,7 +38441,7 @@
         <v>717</v>
       </c>
       <c r="C210" s="11" t="s">
-        <v>1439</v>
+        <v>1469</v>
       </c>
       <c r="D210" s="12"/>
       <c r="E210" s="13" t="s">
@@ -38511,7 +38490,7 @@
         <v>720</v>
       </c>
       <c r="C211" s="11" t="s">
-        <v>1440</v>
+        <v>1421</v>
       </c>
       <c r="D211" s="12"/>
       <c r="E211" s="13" t="s">
@@ -38560,7 +38539,7 @@
         <v>725</v>
       </c>
       <c r="C212" s="11" t="s">
-        <v>1441</v>
+        <v>1422</v>
       </c>
       <c r="D212" s="12"/>
       <c r="E212" s="13" t="s">
@@ -38609,7 +38588,7 @@
         <v>729</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>1440</v>
+        <v>1421</v>
       </c>
       <c r="D213" s="12"/>
       <c r="E213" s="11" t="s">
@@ -38658,7 +38637,7 @@
         <v>735</v>
       </c>
       <c r="C214" s="11" t="s">
-        <v>1442</v>
+        <v>1423</v>
       </c>
       <c r="D214" s="12"/>
       <c r="E214" s="13" t="s">
@@ -38707,7 +38686,7 @@
         <v>742</v>
       </c>
       <c r="C215" s="11" t="s">
-        <v>1443</v>
+        <v>1424</v>
       </c>
       <c r="D215" s="12"/>
       <c r="E215" s="13" t="s">
@@ -38756,7 +38735,7 @@
         <v>746</v>
       </c>
       <c r="C216" s="11" t="s">
-        <v>1444</v>
+        <v>1425</v>
       </c>
       <c r="D216" s="12"/>
       <c r="E216" s="13" t="s">
@@ -38805,7 +38784,7 @@
         <v>750</v>
       </c>
       <c r="C217" s="11" t="s">
-        <v>1445</v>
+        <v>1426</v>
       </c>
       <c r="D217" s="12"/>
       <c r="E217" s="13" t="s">
@@ -38854,7 +38833,7 @@
         <v>754</v>
       </c>
       <c r="C218" s="11" t="s">
-        <v>1446</v>
+        <v>1427</v>
       </c>
       <c r="D218" s="12"/>
       <c r="E218" s="13" t="s">
@@ -38903,7 +38882,7 @@
         <v>759</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>1447</v>
+        <v>1428</v>
       </c>
       <c r="D219" s="12"/>
       <c r="E219" s="13" t="s">
@@ -38952,7 +38931,7 @@
         <v>764</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>1448</v>
+        <v>1429</v>
       </c>
       <c r="D220" s="12"/>
       <c r="E220" s="13" t="s">
@@ -39050,7 +39029,7 @@
         <v>776</v>
       </c>
       <c r="C222" s="11" t="s">
-        <v>1449</v>
+        <v>1459</v>
       </c>
       <c r="D222" s="12"/>
       <c r="E222" s="11" t="s">
@@ -39099,7 +39078,7 @@
         <v>781</v>
       </c>
       <c r="C223" s="11" t="s">
-        <v>1450</v>
+        <v>1459</v>
       </c>
       <c r="D223" s="12"/>
       <c r="E223" s="11" t="s">
@@ -39148,7 +39127,7 @@
         <v>785</v>
       </c>
       <c r="C224" s="11" t="s">
-        <v>1451</v>
+        <v>1459</v>
       </c>
       <c r="D224" s="12"/>
       <c r="E224" s="11" t="s">
@@ -40028,7 +40007,7 @@
         <v>847</v>
       </c>
       <c r="C242" s="11" t="s">
-        <v>1452</v>
+        <v>789</v>
       </c>
       <c r="D242" s="12"/>
       <c r="E242" s="11" t="s">
@@ -40812,7 +40791,7 @@
         <v>906</v>
       </c>
       <c r="C258" s="11" t="s">
-        <v>1453</v>
+        <v>1430</v>
       </c>
       <c r="D258" s="12"/>
       <c r="E258" s="13" t="s">
@@ -40861,7 +40840,7 @@
         <v>912</v>
       </c>
       <c r="C259" s="11" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D259" s="12"/>
       <c r="E259" s="13" t="s">
@@ -40910,7 +40889,7 @@
         <v>919</v>
       </c>
       <c r="C260" s="11" t="s">
-        <v>1455</v>
+        <v>920</v>
       </c>
       <c r="D260" s="12"/>
       <c r="E260" s="13" t="s">
@@ -40959,7 +40938,7 @@
         <v>925</v>
       </c>
       <c r="C261" s="11" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="D261" s="12"/>
       <c r="E261" s="13" t="s">
@@ -41008,7 +40987,7 @@
         <v>930</v>
       </c>
       <c r="C262" s="11" t="s">
-        <v>1457</v>
+        <v>920</v>
       </c>
       <c r="D262" s="12"/>
       <c r="E262" s="13" t="s">
@@ -41057,7 +41036,7 @@
         <v>934</v>
       </c>
       <c r="C263" s="11" t="s">
-        <v>1458</v>
+        <v>935</v>
       </c>
       <c r="D263" s="45"/>
       <c r="E263" s="11" t="s">
@@ -41400,7 +41379,7 @@
         <v>963</v>
       </c>
       <c r="C270" s="11" t="s">
-        <v>1459</v>
+        <v>935</v>
       </c>
       <c r="D270" s="12"/>
       <c r="E270" s="11" t="s">
@@ -41743,7 +41722,7 @@
         <v>990</v>
       </c>
       <c r="C277" s="11" t="s">
-        <v>1460</v>
+        <v>920</v>
       </c>
       <c r="D277" s="12"/>
       <c r="E277" s="11" t="s">
@@ -41792,7 +41771,7 @@
         <v>995</v>
       </c>
       <c r="C278" s="11" t="s">
-        <v>1461</v>
+        <v>920</v>
       </c>
       <c r="D278" s="12"/>
       <c r="E278" s="11" t="s">
@@ -42086,7 +42065,7 @@
         <v>1020</v>
       </c>
       <c r="C284" s="11" t="s">
-        <v>1462</v>
+        <v>1431</v>
       </c>
       <c r="D284" s="12"/>
       <c r="E284" s="13" t="s">
@@ -42135,7 +42114,7 @@
         <v>1025</v>
       </c>
       <c r="C285" s="11" t="s">
-        <v>1463</v>
+        <v>1432</v>
       </c>
       <c r="D285" s="12"/>
       <c r="E285" s="13" t="s">
@@ -42429,7 +42408,7 @@
         <v>1046</v>
       </c>
       <c r="C291" s="11" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="D291" s="12"/>
       <c r="E291" s="11" t="s">
@@ -42821,7 +42800,7 @@
         <v>1079</v>
       </c>
       <c r="C299" s="11" t="s">
-        <v>1465</v>
+        <v>1051</v>
       </c>
       <c r="D299" s="12"/>
       <c r="E299" s="11" t="s">
@@ -42870,7 +42849,7 @@
         <v>1083</v>
       </c>
       <c r="C300" s="11" t="s">
-        <v>1466</v>
+        <v>1051</v>
       </c>
       <c r="D300" s="12"/>
       <c r="E300" s="11" t="s">
@@ -42968,7 +42947,7 @@
         <v>1091</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>1467</v>
+        <v>1051</v>
       </c>
       <c r="D302" s="12"/>
       <c r="E302" s="13" t="s">
@@ -43017,7 +42996,7 @@
         <v>1095</v>
       </c>
       <c r="C303" s="11" t="s">
-        <v>1468</v>
+        <v>1051</v>
       </c>
       <c r="D303" s="12"/>
       <c r="E303" s="11" t="s">
@@ -43409,7 +43388,7 @@
         <v>1126</v>
       </c>
       <c r="C311" s="11" t="s">
-        <v>1469</v>
+        <v>755</v>
       </c>
       <c r="D311" s="12"/>
       <c r="E311" s="11" t="s">
@@ -43458,7 +43437,7 @@
         <v>1130</v>
       </c>
       <c r="C312" s="11" t="s">
-        <v>1470</v>
+        <v>755</v>
       </c>
       <c r="D312" s="12"/>
       <c r="E312" s="11" t="s">
@@ -43948,7 +43927,7 @@
         <v>1172</v>
       </c>
       <c r="C322" s="11" t="s">
-        <v>1471</v>
+        <v>736</v>
       </c>
       <c r="D322" s="12"/>
       <c r="E322" s="11" t="s">
@@ -43997,7 +43976,7 @@
         <v>1176</v>
       </c>
       <c r="C323" s="11" t="s">
-        <v>1472</v>
+        <v>736</v>
       </c>
       <c r="D323" s="12"/>
       <c r="E323" s="13" t="s">
@@ -44291,7 +44270,7 @@
         <v>1202</v>
       </c>
       <c r="C329" s="11" t="s">
-        <v>1386</v>
+        <v>1453</v>
       </c>
       <c r="D329" s="12"/>
       <c r="E329" s="13" t="s">
@@ -44340,7 +44319,7 @@
         <v>1207</v>
       </c>
       <c r="C330" s="11" t="s">
-        <v>1386</v>
+        <v>1454</v>
       </c>
       <c r="D330" s="12"/>
       <c r="E330" s="13" t="s">
@@ -44389,7 +44368,7 @@
         <v>1211</v>
       </c>
       <c r="C331" s="11" t="s">
-        <v>1386</v>
+        <v>1455</v>
       </c>
       <c r="D331" s="12"/>
       <c r="E331" s="13" t="s">
@@ -44438,7 +44417,7 @@
         <v>1216</v>
       </c>
       <c r="C332" s="11" t="s">
-        <v>1386</v>
+        <v>1456</v>
       </c>
       <c r="D332" s="12"/>
       <c r="E332" s="13" t="s">
@@ -44487,7 +44466,7 @@
         <v>1220</v>
       </c>
       <c r="C333" s="11" t="s">
-        <v>1386</v>
+        <v>1457</v>
       </c>
       <c r="D333" s="12"/>
       <c r="E333" s="13" t="s">
@@ -44536,7 +44515,7 @@
         <v>1223</v>
       </c>
       <c r="C334" s="11" t="s">
-        <v>1386</v>
+        <v>1458</v>
       </c>
       <c r="D334" s="12"/>
       <c r="E334" s="13" t="s">
@@ -44977,7 +44956,7 @@
         <v>1266</v>
       </c>
       <c r="C343" s="11" t="s">
-        <v>1473</v>
+        <v>1464</v>
       </c>
       <c r="D343" s="12"/>
       <c r="E343" s="11" t="s">
@@ -45418,7 +45397,7 @@
         <v>1298</v>
       </c>
       <c r="C352" s="11" t="s">
-        <v>1474</v>
+        <v>1271</v>
       </c>
       <c r="D352" s="50"/>
       <c r="E352" s="13" t="s">
@@ -45467,7 +45446,7 @@
         <v>1301</v>
       </c>
       <c r="C353" s="11" t="s">
-        <v>1475</v>
+        <v>1271</v>
       </c>
       <c r="D353" s="50"/>
       <c r="E353" s="13" t="s">
@@ -45516,7 +45495,7 @@
         <v>1304</v>
       </c>
       <c r="C354" s="11" t="s">
-        <v>1476</v>
+        <v>1271</v>
       </c>
       <c r="D354" s="50"/>
       <c r="E354" s="13" t="s">
@@ -45565,7 +45544,7 @@
         <v>1307</v>
       </c>
       <c r="C355" s="11" t="s">
-        <v>1477</v>
+        <v>1271</v>
       </c>
       <c r="D355" s="50"/>
       <c r="E355" s="13" t="s">
@@ -45614,7 +45593,7 @@
         <v>1310</v>
       </c>
       <c r="C356" s="11" t="s">
-        <v>1478</v>
+        <v>1271</v>
       </c>
       <c r="D356" s="50"/>
       <c r="E356" s="13" t="s">
@@ -45663,7 +45642,7 @@
         <v>1313</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>1479</v>
+        <v>1271</v>
       </c>
       <c r="D357" s="50"/>
       <c r="E357" s="13" t="s">
@@ -45761,7 +45740,7 @@
         <v>1319</v>
       </c>
       <c r="C359" s="11" t="s">
-        <v>1271</v>
+        <v>1472</v>
       </c>
       <c r="D359" s="50"/>
       <c r="E359" s="13" t="s">
